--- a/output_excel/hosp3_resultados.xlsx
+++ b/output_excel/hosp3_resultados.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flopes\Documents\GitHub\Doutorado-real-datasets\output_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="SVM" sheetId="1" r:id="rId1"/>
-    <sheet name="GB" sheetId="2" r:id="rId2"/>
-    <sheet name="RF" sheetId="3" r:id="rId3"/>
+    <sheet name="(a) Gradient Boosting" sheetId="2" r:id="rId1"/>
+    <sheet name="(b) Random Forest" sheetId="3" r:id="rId2"/>
+    <sheet name="(c) Support Vector Machine" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -72,8 +77,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +141,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -180,9 +193,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -214,9 +227,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,11 +438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,145 +486,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7369566764125296</v>
+        <v>0.74201547424626757</v>
       </c>
       <c r="C2">
-        <v>0.02335266118107542</v>
+        <v>3.9735789498863881E-2</v>
       </c>
       <c r="D2">
-        <v>0.7372303672155127</v>
+        <v>0.74192580072440395</v>
       </c>
       <c r="E2">
-        <v>0.01996790096425626</v>
+        <v>3.3736593876039743E-2</v>
       </c>
       <c r="F2">
-        <v>0.7172739381725102</v>
+        <v>0.59092661398274871</v>
       </c>
       <c r="G2">
-        <v>0.03425058933024194</v>
+        <v>6.4323019979363821E-2</v>
       </c>
       <c r="H2">
-        <v>0.7422297425867738</v>
+        <v>0.75959260969059783</v>
       </c>
       <c r="I2">
-        <v>0.0225017800584522</v>
+        <v>4.0150414057067318E-2</v>
       </c>
       <c r="J2">
-        <v>0.7361409650555382</v>
+        <v>0.74138551754834459</v>
       </c>
       <c r="K2">
-        <v>0.02055708263982616</v>
+        <v>4.1220574468119248E-2</v>
       </c>
       <c r="L2">
-        <v>0.7361247247083275</v>
+        <v>0.73363069797918123</v>
       </c>
       <c r="M2">
-        <v>0.0206994936790885</v>
+        <v>3.8941063036986787E-2</v>
       </c>
       <c r="N2">
-        <v>0.7385563051100423</v>
+        <v>0.74551487609185929</v>
       </c>
       <c r="O2">
-        <v>0.0213052998279599</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>3.7760600669340477E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.682282120395328</v>
+        <v>0.66352201257861632</v>
       </c>
       <c r="C3">
-        <v>0.04551361905002263</v>
+        <v>4.3459984154356132E-2</v>
       </c>
       <c r="D3">
-        <v>0.6785085354896676</v>
+        <v>0.68422282120395328</v>
       </c>
       <c r="E3">
-        <v>0.05286148079134348</v>
+        <v>4.0750541325784879E-2</v>
       </c>
       <c r="F3">
-        <v>0.5933872416891285</v>
+        <v>0.74300089847259654</v>
       </c>
       <c r="G3">
-        <v>0.07220203155464869</v>
+        <v>6.9750112216396182E-2</v>
       </c>
       <c r="H3">
-        <v>0.6804312668463612</v>
+        <v>0.69378256963162621</v>
       </c>
       <c r="I3">
-        <v>0.03968246396213539</v>
+        <v>3.214582523027848E-2</v>
       </c>
       <c r="J3">
-        <v>0.6747349505840072</v>
+        <v>0.66734950584007191</v>
       </c>
       <c r="K3">
-        <v>0.05220235581143726</v>
+        <v>3.0903905017448819E-2</v>
       </c>
       <c r="L3">
-        <v>0.6747349505840072</v>
+        <v>0.66923629829290199</v>
       </c>
       <c r="M3">
-        <v>0.05220235581143726</v>
+        <v>2.9924303912194881E-2</v>
       </c>
       <c r="N3">
-        <v>0.6898831985624438</v>
+        <v>0.66163522012578613</v>
       </c>
       <c r="O3">
-        <v>0.06016113064485468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>3.413072591500662E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6545181092694905</v>
+        <v>0.6755310006138735</v>
       </c>
       <c r="C4">
-        <v>0.04159730736340696</v>
+        <v>5.0284854574978152E-2</v>
       </c>
       <c r="D4">
-        <v>0.6722897483118478</v>
+        <v>0.67332719459791279</v>
       </c>
       <c r="E4">
-        <v>0.04248939812032797</v>
+        <v>2.8860104280992189E-2</v>
       </c>
       <c r="F4">
-        <v>0.6965745856353591</v>
+        <v>0.38861878453038667</v>
       </c>
       <c r="G4">
-        <v>0.0336409814284059</v>
+        <v>0.10576108832573471</v>
       </c>
       <c r="H4">
-        <v>0.6722774708410068</v>
+        <v>0.69765500306936779</v>
       </c>
       <c r="I4">
-        <v>0.03424645148631024</v>
+        <v>5.3938819773397872E-2</v>
       </c>
       <c r="J4">
-        <v>0.6711970534069982</v>
+        <v>0.68440761203192146</v>
       </c>
       <c r="K4">
-        <v>0.05107126088973606</v>
+        <v>3.7582643530186019E-2</v>
       </c>
       <c r="L4">
-        <v>0.6700920810313076</v>
+        <v>0.67446899938612648</v>
       </c>
       <c r="M4">
-        <v>0.05179627628388747</v>
+        <v>4.3058111599443359E-2</v>
       </c>
       <c r="N4">
-        <v>0.6667526089625537</v>
+        <v>0.68103744628606511</v>
       </c>
       <c r="O4">
-        <v>0.04525870584861771</v>
+        <v>4.4894077198937253E-2</v>
       </c>
     </row>
   </sheetData>
@@ -618,11 +633,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,145 +681,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7420154742462676</v>
+        <v>0.75139859752233362</v>
       </c>
       <c r="C2">
-        <v>0.03973578949886388</v>
+        <v>2.8948932383798389E-2</v>
       </c>
       <c r="D2">
-        <v>0.7419258007244039</v>
+        <v>0.75424819519523989</v>
       </c>
       <c r="E2">
-        <v>0.03373659387603974</v>
+        <v>2.9586213082278039E-2</v>
       </c>
       <c r="F2">
-        <v>0.5909266139827487</v>
+        <v>0.57162911861989318</v>
       </c>
       <c r="G2">
-        <v>0.06432301997936382</v>
+        <v>5.8360953852106608E-2</v>
       </c>
       <c r="H2">
-        <v>0.7595926096905978</v>
+        <v>0.75465395567866123</v>
       </c>
       <c r="I2">
-        <v>0.04015041405706732</v>
+        <v>2.2343103077907829E-2</v>
       </c>
       <c r="J2">
-        <v>0.7413855175483446</v>
+        <v>0.75303031807253618</v>
       </c>
       <c r="K2">
-        <v>0.04122057446811925</v>
+        <v>2.6954956665377009E-2</v>
       </c>
       <c r="L2">
-        <v>0.7336306979791812</v>
+        <v>0.75273469907786605</v>
       </c>
       <c r="M2">
-        <v>0.03894106303698679</v>
+        <v>2.8533137487957529E-2</v>
       </c>
       <c r="N2">
-        <v>0.7455148760918593</v>
+        <v>0.75525669345538005</v>
       </c>
       <c r="O2">
-        <v>0.03776060066934048</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.3033356694525761E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6635220125786163</v>
+        <v>0.66921832884097043</v>
       </c>
       <c r="C3">
-        <v>0.04345998415435613</v>
+        <v>5.5174945386577537E-2</v>
       </c>
       <c r="D3">
-        <v>0.6842228212039533</v>
+        <v>0.67865229110512126</v>
       </c>
       <c r="E3">
-        <v>0.04075054132578488</v>
+        <v>3.5752865293937078E-2</v>
       </c>
       <c r="F3">
-        <v>0.7430008984725965</v>
+        <v>0.7183468104222821</v>
       </c>
       <c r="G3">
-        <v>0.06975011221639618</v>
+        <v>8.979862565130721E-2</v>
       </c>
       <c r="H3">
-        <v>0.6937825696316262</v>
+        <v>0.70134770889487874</v>
       </c>
       <c r="I3">
-        <v>0.03214582523027848</v>
+        <v>2.9963421247500781E-2</v>
       </c>
       <c r="J3">
-        <v>0.6673495058400719</v>
+        <v>0.68059299191374667</v>
       </c>
       <c r="K3">
-        <v>0.03090390501744882</v>
+        <v>4.1844136647601143E-2</v>
       </c>
       <c r="L3">
-        <v>0.669236298292902</v>
+        <v>0.69002695417789761</v>
       </c>
       <c r="M3">
-        <v>0.02992430391219488</v>
+        <v>4.5062677890297852E-2</v>
       </c>
       <c r="N3">
-        <v>0.6616352201257861</v>
+        <v>0.69561545372866118</v>
       </c>
       <c r="O3">
-        <v>0.03413072591500662</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>3.6552676712953258E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6755310006138735</v>
+        <v>0.67777777777777781</v>
       </c>
       <c r="C4">
-        <v>0.05028485457497815</v>
+        <v>3.117479738410708E-2</v>
       </c>
       <c r="D4">
-        <v>0.6733271945979128</v>
+        <v>0.68333947206875378</v>
       </c>
       <c r="E4">
-        <v>0.02886010428099219</v>
+        <v>2.7204039949050358E-2</v>
       </c>
       <c r="F4">
-        <v>0.3886187845303867</v>
+        <v>0.40743400859422962</v>
       </c>
       <c r="G4">
-        <v>0.1057610883257347</v>
+        <v>0.1156397725208799</v>
       </c>
       <c r="H4">
-        <v>0.6976550030693678</v>
+        <v>0.66558011049723753</v>
       </c>
       <c r="I4">
-        <v>0.05393881977339787</v>
+        <v>2.392271966920316E-2</v>
       </c>
       <c r="J4">
-        <v>0.6844076120319215</v>
+        <v>0.6744567219152855</v>
       </c>
       <c r="K4">
-        <v>0.03758264353018602</v>
+        <v>2.6941429933648949E-2</v>
       </c>
       <c r="L4">
-        <v>0.6744689993861265</v>
+        <v>0.67555555555555569</v>
       </c>
       <c r="M4">
-        <v>0.04305811159944336</v>
+        <v>2.7647742601767292E-2</v>
       </c>
       <c r="N4">
-        <v>0.6810374462860651</v>
+        <v>0.67775322283609574</v>
       </c>
       <c r="O4">
-        <v>0.04489407719893725</v>
+        <v>2.946322341518454E-2</v>
       </c>
     </row>
   </sheetData>
@@ -813,11 +828,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,145 +876,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7513985975223336</v>
+        <v>0.7369566764125296</v>
       </c>
       <c r="C2">
-        <v>0.02894893238379839</v>
+        <v>2.3352661181075419E-2</v>
       </c>
       <c r="D2">
-        <v>0.7542481951952399</v>
+        <v>0.73723036721551272</v>
       </c>
       <c r="E2">
-        <v>0.02958621308227804</v>
+        <v>1.9967900964256258E-2</v>
       </c>
       <c r="F2">
-        <v>0.5716291186198932</v>
+        <v>0.71727393817251017</v>
       </c>
       <c r="G2">
-        <v>0.05836095385210661</v>
+        <v>3.4250589330241943E-2</v>
       </c>
       <c r="H2">
-        <v>0.7546539556786612</v>
+        <v>0.74222974258677377</v>
       </c>
       <c r="I2">
-        <v>0.02234310307790783</v>
+        <v>2.25017800584522E-2</v>
       </c>
       <c r="J2">
-        <v>0.7530303180725362</v>
+        <v>0.73614096505553817</v>
       </c>
       <c r="K2">
-        <v>0.02695495666537701</v>
+        <v>2.0557082639826162E-2</v>
       </c>
       <c r="L2">
-        <v>0.7527346990778661</v>
+        <v>0.73612472470832746</v>
       </c>
       <c r="M2">
-        <v>0.02853313748795753</v>
+        <v>2.06994936790885E-2</v>
       </c>
       <c r="N2">
-        <v>0.75525669345538</v>
+        <v>0.73855630511004233</v>
       </c>
       <c r="O2">
-        <v>0.02303335669452576</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.1305299827959898E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6692183288409704</v>
+        <v>0.68228212039532798</v>
       </c>
       <c r="C3">
-        <v>0.05517494538657754</v>
+        <v>4.551361905002263E-2</v>
       </c>
       <c r="D3">
-        <v>0.6786522911051213</v>
+        <v>0.67850853548966761</v>
       </c>
       <c r="E3">
-        <v>0.03575286529393708</v>
+        <v>5.2861480791343479E-2</v>
       </c>
       <c r="F3">
-        <v>0.7183468104222821</v>
+        <v>0.59338724168912849</v>
       </c>
       <c r="G3">
-        <v>0.08979862565130721</v>
+        <v>7.2202031554648688E-2</v>
       </c>
       <c r="H3">
-        <v>0.7013477088948787</v>
+        <v>0.68043126684636124</v>
       </c>
       <c r="I3">
-        <v>0.02996342124750078</v>
+        <v>3.9682463962135393E-2</v>
       </c>
       <c r="J3">
-        <v>0.6805929919137467</v>
+        <v>0.67473495058400723</v>
       </c>
       <c r="K3">
-        <v>0.04184413664760114</v>
+        <v>5.2202355811437257E-2</v>
       </c>
       <c r="L3">
-        <v>0.6900269541778976</v>
+        <v>0.67473495058400723</v>
       </c>
       <c r="M3">
-        <v>0.04506267789029785</v>
+        <v>5.2202355811437257E-2</v>
       </c>
       <c r="N3">
-        <v>0.6956154537286612</v>
+        <v>0.68988319856244384</v>
       </c>
       <c r="O3">
-        <v>0.03655267671295326</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>6.0161130644854677E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6777777777777778</v>
+        <v>0.6545181092694905</v>
       </c>
       <c r="C4">
-        <v>0.03117479738410708</v>
+        <v>4.1597307363406957E-2</v>
       </c>
       <c r="D4">
-        <v>0.6833394720687538</v>
+        <v>0.67228974831184785</v>
       </c>
       <c r="E4">
-        <v>0.02720403994905036</v>
+        <v>4.2489398120327967E-2</v>
       </c>
       <c r="F4">
-        <v>0.4074340085942296</v>
+        <v>0.69657458563535912</v>
       </c>
       <c r="G4">
-        <v>0.1156397725208799</v>
+        <v>3.3640981428405901E-2</v>
       </c>
       <c r="H4">
-        <v>0.6655801104972375</v>
+        <v>0.67227747084100675</v>
       </c>
       <c r="I4">
-        <v>0.02392271966920316</v>
+        <v>3.4246451486310239E-2</v>
       </c>
       <c r="J4">
-        <v>0.6744567219152855</v>
+        <v>0.6711970534069982</v>
       </c>
       <c r="K4">
-        <v>0.02694142993364895</v>
+        <v>5.1071260889736063E-2</v>
       </c>
       <c r="L4">
-        <v>0.6755555555555557</v>
+        <v>0.67009208103130757</v>
       </c>
       <c r="M4">
-        <v>0.02764774260176729</v>
+        <v>5.1796276283887471E-2</v>
       </c>
       <c r="N4">
-        <v>0.6777532228360957</v>
+        <v>0.66675260896255373</v>
       </c>
       <c r="O4">
-        <v>0.02946322341518454</v>
+        <v>4.5258705848617707E-2</v>
       </c>
     </row>
   </sheetData>
